--- a/height_data.xlsx
+++ b/height_data.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/Linaria_specProj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC784297-13A1-3748-8443-D86FEE6AA5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735BBB37-B125-F24A-8939-9ECACDCD8549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
+    <workbookView xWindow="4080" yWindow="1600" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
   </bookViews>
   <sheets>
     <sheet name="D1 3 2 26" sheetId="2" r:id="rId1"/>
     <sheet name="D2 3 3 26" sheetId="1" r:id="rId2"/>
     <sheet name="D3 3 9 26" sheetId="3" r:id="rId3"/>
     <sheet name="check" sheetId="4" r:id="rId4"/>
+    <sheet name="D4 3 16 26" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="91">
   <si>
     <t>lc1</t>
   </si>
@@ -282,6 +283,36 @@
   </si>
   <si>
     <t>measured</t>
+  </si>
+  <si>
+    <t>plant</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>tall</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>bush</t>
+  </si>
+  <si>
+    <t>s_1 is main height + sprouts</t>
+  </si>
+  <si>
+    <t>no sprouts</t>
+  </si>
+  <si>
+    <t>bush_score</t>
+  </si>
+  <si>
+    <t>s_1 is main height + sprouts, top of non-side side stem broke</t>
   </si>
 </sst>
 </file>
@@ -4053,7 +4084,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBC2FB9-9962-DE4D-94E8-8542EC40DA6E}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -4080,7 +4111,1334 @@
         <v>42</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D720C2A-106B-0F4C-ADF0-DF0528C1EF06}">
+  <dimension ref="A1:S40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="17" width="6" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>45+7.2</f>
+        <v>52.2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>50.5</v>
+      </c>
+      <c r="F2" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>41.4</v>
+      </c>
+      <c r="H2" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J2" s="2">
+        <f>45+13.5</f>
+        <v>58.5</v>
+      </c>
+      <c r="K2" s="2">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="L2" s="2">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="N2" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>3</v>
+      </c>
+      <c r="P2" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <f>45+8.2</f>
+        <v>53.2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F3" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>51.3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="K3" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.7</v>
+      </c>
+      <c r="M3" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="N3" s="2">
+        <v>45.2</v>
+      </c>
+      <c r="O3" s="2">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>41.8</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="G4" s="2">
+        <v>42.8</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="J4" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="K4" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="L4" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="M4" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="O4" s="2">
+        <v>28</v>
+      </c>
+      <c r="P4" s="2">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>45+7.9</f>
+        <v>52.9</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="H5" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="K5" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="L5" s="2">
+        <v>50.5</v>
+      </c>
+      <c r="M5" s="2">
+        <v>48</v>
+      </c>
+      <c r="N5" s="2">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>45+27.1</f>
+        <v>72.099999999999994</v>
+      </c>
+      <c r="E6" s="2">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8</v>
+      </c>
+      <c r="H7" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="I7" s="2">
+        <v>41.5</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="S7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>7.9</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="S9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f>45+16.5</f>
+        <v>61.5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>6.9</v>
+      </c>
+      <c r="E11" s="2">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="F11" s="2">
+        <v>42.2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="J11" s="2">
+        <v>22.2</v>
+      </c>
+      <c r="S11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="E12" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>55.3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F13" s="2">
+        <f>45+8.9</f>
+        <v>53.9</v>
+      </c>
+      <c r="G13" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0.5</v>
+      </c>
+      <c r="D15">
+        <v>50.3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>8.9</v>
+      </c>
+      <c r="E16" s="2">
+        <v>27.2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>25.3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>29.9</v>
+      </c>
+      <c r="H16" s="2">
+        <v>29.7</v>
+      </c>
+      <c r="I16" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J16" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="K16" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="L16" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="M16" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="S16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2">
+        <v>20.6</v>
+      </c>
+      <c r="F17" s="2">
+        <f>45+28.1</f>
+        <v>73.099999999999994</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="E18" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="F18" s="2">
+        <v>26</v>
+      </c>
+      <c r="G18" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>22.4</v>
+      </c>
+      <c r="I18" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="J18" s="2">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>24.5</v>
+      </c>
+      <c r="E19" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>10.9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>41.4</v>
+      </c>
+      <c r="F20" s="2">
+        <f>45+9.1</f>
+        <v>54.1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>54</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>52</v>
+      </c>
+      <c r="G21" s="2">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>7.5</v>
+      </c>
+      <c r="E22" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F22" s="2">
+        <v>31.6</v>
+      </c>
+      <c r="G22" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="H22" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="S22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>45+12.6</f>
+        <v>57.6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="G23" s="2">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>8.5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="G24" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="S24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f>45+17.2</f>
+        <v>62.2</v>
+      </c>
+      <c r="E25" s="2">
+        <f>45+15.3</f>
+        <v>60.3</v>
+      </c>
+      <c r="F25" s="2">
+        <f>45+15.6</f>
+        <v>60.6</v>
+      </c>
+      <c r="G25" s="2">
+        <v>29.9</v>
+      </c>
+      <c r="H25" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26">
+        <v>0.5</v>
+      </c>
+      <c r="D26">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="E26" s="2">
+        <v>33</v>
+      </c>
+      <c r="F26" s="2">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="G26" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="H26" s="2">
+        <f>45+8.4</f>
+        <v>53.4</v>
+      </c>
+      <c r="I26" s="2">
+        <v>39</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>45.6</v>
+      </c>
+      <c r="E27" s="2">
+        <v>20.6</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>8.1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="F29" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="G29" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="H29" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="I29" s="2">
+        <v>41.8</v>
+      </c>
+      <c r="J29" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="L29" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="M29" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="S29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <f>45+15.1</f>
+        <v>60.1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>27.7</v>
+      </c>
+      <c r="F30" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="H30" s="2">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="I30" s="2">
+        <v>26.2</v>
+      </c>
+      <c r="J30" s="2">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31">
+        <v>0.5</v>
+      </c>
+      <c r="D31">
+        <v>24.1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F32" s="2">
+        <v>21</v>
+      </c>
+      <c r="G32" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="I32" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="J32" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="K32" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="L32" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="M32" s="2">
+        <v>7.3</v>
+      </c>
+      <c r="S32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>9.6</v>
+      </c>
+      <c r="E33" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>38.9</v>
+      </c>
+      <c r="G33" s="2">
+        <v>25.7</v>
+      </c>
+      <c r="H33" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="I33" s="2">
+        <v>27.2</v>
+      </c>
+      <c r="J33" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="K33" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="S33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>50.1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="F34" s="2">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G34" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="H34" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="I34" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="J34" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="K34" s="2">
+        <f>45+9.4</f>
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f>45+35.8</f>
+        <v>80.8</v>
+      </c>
+      <c r="E35" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F35" s="2">
+        <v>44.8</v>
+      </c>
+      <c r="G35" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H35" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="I35" s="2">
+        <f>45+20.4</f>
+        <v>65.400000000000006</v>
+      </c>
+      <c r="J35" s="2">
+        <f>45+16.8</f>
+        <v>61.8</v>
+      </c>
+      <c r="K35" s="2">
+        <v>45.8</v>
+      </c>
+      <c r="L35" s="2">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f>45+10.2</f>
+        <v>55.2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>38</v>
+      </c>
+      <c r="F36" s="2">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="G36" s="2">
+        <v>36</v>
+      </c>
+      <c r="H36" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="I36" s="2">
+        <v>33.9</v>
+      </c>
+      <c r="J36" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="K36" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="L36" s="2">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E37" s="2">
+        <v>28.3</v>
+      </c>
+      <c r="F37" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="H37" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I37" s="2">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J37" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K37" s="2">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>8.6</v>
+      </c>
+      <c r="E38" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G38" s="2">
+        <v>23.3</v>
+      </c>
+      <c r="H38" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="I38" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="J38" s="2">
+        <v>25.8</v>
+      </c>
+      <c r="K38" s="2">
+        <v>23</v>
+      </c>
+      <c r="L38" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="S38" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f>45+8.4</f>
+        <v>53.4</v>
+      </c>
+      <c r="E39" s="2">
+        <v>29</v>
+      </c>
+      <c r="F39" s="2">
+        <v>21.1</v>
+      </c>
+      <c r="G39" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="H39" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="I39" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="J39" s="2">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="K39" s="2">
+        <f>45+3.5</f>
+        <v>48.5</v>
+      </c>
+      <c r="L39" s="2">
+        <v>31</v>
+      </c>
+      <c r="M39" s="2">
+        <v>20.6</v>
+      </c>
+      <c r="N39" s="2">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>8.5</v>
+      </c>
+      <c r="E40" s="2">
+        <v>24.2</v>
+      </c>
+      <c r="F40" s="2">
+        <v>30</v>
+      </c>
+      <c r="G40" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H40" s="2">
+        <v>29.4</v>
+      </c>
+      <c r="I40" s="2">
+        <v>27</v>
+      </c>
+      <c r="J40" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="K40" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="L40" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="S40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/height_data.xlsx
+++ b/height_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/Linaria_specProj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735BBB37-B125-F24A-8939-9ECACDCD8549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806A1CD9-7B11-6D48-BF1D-30CCBACAC980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1600" windowWidth="30240" windowHeight="18980" activeTab="4" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
   </bookViews>
   <sheets>
     <sheet name="D1 3 2 26" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="D3 3 9 26" sheetId="3" r:id="rId3"/>
     <sheet name="check" sheetId="4" r:id="rId4"/>
     <sheet name="D4 3 16 26" sheetId="5" r:id="rId5"/>
+    <sheet name="D5 3 23 26" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>lc1</t>
   </si>
@@ -313,6 +314,9 @@
   </si>
   <si>
     <t>s_1 is main height + sprouts, top of non-side side stem broke</t>
+  </si>
+  <si>
+    <t>bush score</t>
   </si>
 </sst>
 </file>
@@ -422,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -459,6 +463,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4203,7 +4210,9 @@
       <c r="Q1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="2"/>
+      <c r="S1" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
@@ -5434,6 +5443,788 @@
       </c>
       <c r="S40" t="s">
         <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35664989-61A4-F94C-A05A-9E3D17A531B3}">
+  <dimension ref="A1:O32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="4" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E2" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="F2">
+        <v>81.3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>16</v>
+      </c>
+      <c r="O2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="E4" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>8.1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>73.7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>84.3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>7.3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>24.3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>56.5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="H7" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2.8</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>30.6</v>
+      </c>
+      <c r="E8" s="2">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F8" s="2">
+        <v>29.4</v>
+      </c>
+      <c r="G8" s="2">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E9" s="2">
+        <v>25.4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>30.8</v>
+      </c>
+      <c r="H9" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="L9" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="M9" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>58.9</v>
+      </c>
+      <c r="E11" s="2">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>26.8</v>
+      </c>
+      <c r="E12" s="2">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>36.1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>35</v>
+      </c>
+      <c r="F13" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="G13" s="2">
+        <v>29</v>
+      </c>
+      <c r="H13" s="2">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="I13" s="2">
+        <v>29</v>
+      </c>
+      <c r="J13" s="2">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2">
+        <v>47.7</v>
+      </c>
+      <c r="F14" s="2">
+        <v>60.6</v>
+      </c>
+      <c r="G14" s="2">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E15" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F15" s="2">
+        <v>44.2</v>
+      </c>
+      <c r="G15" s="2">
+        <v>27.2</v>
+      </c>
+      <c r="H15" s="2">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>61.4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>35.6</v>
+      </c>
+      <c r="F16" s="2">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>77.3</v>
+      </c>
+      <c r="E17" s="2">
+        <v>80.3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>31.6</v>
+      </c>
+      <c r="G17" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>74</v>
+      </c>
+      <c r="E18" s="2">
+        <v>31</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G18" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>8.5</v>
+      </c>
+      <c r="E19" s="2">
+        <v>30.1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="O19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="E21" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>44.8</v>
+      </c>
+      <c r="G21" s="2">
+        <v>51.3</v>
+      </c>
+      <c r="H21" s="2">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="I21" s="2">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>49.4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>7.9</v>
+      </c>
+      <c r="E23" s="2">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2">
+        <v>6.3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>46.2</v>
+      </c>
+      <c r="H23" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I23" s="2">
+        <v>13.6</v>
+      </c>
+      <c r="J23" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="K23" s="2">
+        <v>25.1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>25.6</v>
+      </c>
+      <c r="E24" s="2">
+        <v>28</v>
+      </c>
+      <c r="F24" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="G24" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="J24" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="K24" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>50.6</v>
+      </c>
+      <c r="E25" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="F25" s="2">
+        <v>27.3</v>
+      </c>
+      <c r="G25" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="H25" s="2">
+        <v>62.8</v>
+      </c>
+      <c r="I25" s="2">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>9.6</v>
+      </c>
+      <c r="E26" s="2">
+        <v>29.1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>22.9</v>
+      </c>
+      <c r="G26" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="H26" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="K26" s="2">
+        <v>12</v>
+      </c>
+      <c r="L26" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="M26" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="N26" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>89.6</v>
+      </c>
+      <c r="E27" s="2">
+        <v>51.4</v>
+      </c>
+      <c r="F27" s="2">
+        <v>54.9</v>
+      </c>
+      <c r="G27" s="2">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="H27" s="2">
+        <v>68.7</v>
+      </c>
+      <c r="I27" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="J27" s="2">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>73.7</v>
+      </c>
+      <c r="E28" s="2">
+        <v>59.7</v>
+      </c>
+      <c r="F28" s="2">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="G28" s="2">
+        <v>17.8</v>
+      </c>
+      <c r="H28" s="2">
+        <v>26.2</v>
+      </c>
+      <c r="I28" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2">
+        <v>23.3</v>
+      </c>
+      <c r="F29" s="2">
+        <v>43.8</v>
+      </c>
+      <c r="G29" s="2">
+        <v>32</v>
+      </c>
+      <c r="H29" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="I29" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="J29" s="2">
+        <v>29.1</v>
+      </c>
+      <c r="K29" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="O29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>51.2</v>
+      </c>
+      <c r="E30" s="2">
+        <v>33.9</v>
+      </c>
+      <c r="F30" s="2">
+        <v>45</v>
+      </c>
+      <c r="G30" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="H30" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I30" s="2">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2">
+        <v>39.6</v>
+      </c>
+      <c r="F31" s="2">
+        <v>41.7</v>
+      </c>
+      <c r="G31" s="2">
+        <v>28.7</v>
+      </c>
+      <c r="H31" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="O31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/height_data.xlsx
+++ b/height_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/Linaria_specProj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806A1CD9-7B11-6D48-BF1D-30CCBACAC980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578A45BC-1BD2-AA4D-865C-783A34B81A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>lc1</t>
   </si>
@@ -5454,7 +5454,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35664989-61A4-F94C-A05A-9E3D17A531B3}">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.1640625" bestFit="1" customWidth="1"/>
@@ -6226,6 +6226,292 @@
       <c r="C32">
         <v>0</v>
       </c>
+      <c r="D32">
+        <v>62.8</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45.1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>45.7</v>
+      </c>
+      <c r="G32" s="2">
+        <v>54.4</v>
+      </c>
+      <c r="H32" s="2">
+        <v>54.2</v>
+      </c>
+      <c r="I32" s="2">
+        <v>24.1</v>
+      </c>
+      <c r="J32" s="2">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="F33" s="2">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G33" s="2">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="J33" s="2">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="K33" s="2">
+        <v>25.6</v>
+      </c>
+      <c r="L33" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="O33" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>66</v>
+      </c>
+      <c r="E34" s="2">
+        <v>26.2</v>
+      </c>
+      <c r="F34" s="2">
+        <v>31.6</v>
+      </c>
+      <c r="G34" s="2">
+        <v>48.6</v>
+      </c>
+      <c r="H34" s="2">
+        <v>62.4</v>
+      </c>
+      <c r="I34" s="2">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="J34" s="2">
+        <v>31.1</v>
+      </c>
+      <c r="K34" s="2">
+        <v>44.4</v>
+      </c>
+      <c r="L34" s="2">
+        <v>31.9</v>
+      </c>
+      <c r="M34" s="2">
+        <v>43.6</v>
+      </c>
+      <c r="N34" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>58.5</v>
+      </c>
+      <c r="E35" s="2">
+        <v>48.5</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G35" s="2">
+        <v>8</v>
+      </c>
+      <c r="H35" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="I35" s="2">
+        <v>65</v>
+      </c>
+      <c r="J35" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="K35" s="2">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>60.2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>58.5</v>
+      </c>
+      <c r="F36" s="2">
+        <v>33.6</v>
+      </c>
+      <c r="G36" s="2">
+        <v>52.2</v>
+      </c>
+      <c r="H36" s="2">
+        <v>39.4</v>
+      </c>
+      <c r="I36" s="2">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="J36" s="2">
+        <v>46.7</v>
+      </c>
+      <c r="K36" s="2">
+        <v>66</v>
+      </c>
+      <c r="L36" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="M36" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E37" s="2">
+        <v>31.1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>14</v>
+      </c>
+      <c r="G37" s="2">
+        <v>50.8</v>
+      </c>
+      <c r="H37" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="J37" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="K37" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="O37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>59</v>
+      </c>
+      <c r="E38" s="2">
+        <v>30.4</v>
+      </c>
+      <c r="F38" s="2">
+        <v>50.1</v>
+      </c>
+      <c r="G38" s="2">
+        <v>48.8</v>
+      </c>
+      <c r="H38" s="2">
+        <v>37.6</v>
+      </c>
+      <c r="I38" s="2">
+        <v>58.1</v>
+      </c>
+      <c r="J38" s="2">
+        <v>42.2</v>
+      </c>
+      <c r="K38" s="2">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>52.4</v>
+      </c>
+      <c r="E39" s="2">
+        <v>51.6</v>
+      </c>
+      <c r="F39" s="2">
+        <v>47.4</v>
+      </c>
+      <c r="G39" s="2">
+        <v>46.1</v>
+      </c>
+      <c r="H39" s="2">
+        <v>22.1</v>
+      </c>
+      <c r="I39" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="J39" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="K39" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="L39" s="2">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="E40" s="2">
+        <v>26.8</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/height_data.xlsx
+++ b/height_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/Linaria_specProj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578A45BC-1BD2-AA4D-865C-783A34B81A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3292A9-F21C-C242-A0C8-499AB893419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
   </bookViews>
   <sheets>
     <sheet name="D1 3 2 26" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="check" sheetId="4" r:id="rId4"/>
     <sheet name="D4 3 16 26" sheetId="5" r:id="rId5"/>
     <sheet name="D5 3 23 26" sheetId="6" r:id="rId6"/>
+    <sheet name="meta_data" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="94">
   <si>
     <t>lc1</t>
   </si>
@@ -160,15 +161,9 @@
     <t>date</t>
   </si>
   <si>
-    <t>cl10</t>
-  </si>
-  <si>
     <t>c11</t>
   </si>
   <si>
-    <t>plantid</t>
-  </si>
-  <si>
     <t>main_height</t>
   </si>
   <si>
@@ -286,9 +281,6 @@
     <t>measured</t>
   </si>
   <si>
-    <t>plant</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -317,6 +309,21 @@
   </si>
   <si>
     <t>bush score</t>
+  </si>
+  <si>
+    <t>plant_id</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>holepunch</t>
+  </si>
+  <si>
+    <t>tophalf</t>
   </si>
 </sst>
 </file>
@@ -814,30 +821,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B1" s="10">
         <v>0.35833333333333334</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" s="11">
         <v>0.46180555555555558</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="9"/>
     </row>
@@ -846,19 +853,19 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -980,7 +987,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -1073,7 +1080,7 @@
         <v>46083</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2">
         <v>24.3</v>
@@ -1119,7 +1126,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1173,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1278,7 +1285,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1451,7 +1458,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -1488,7 +1495,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1496,7 +1503,7 @@
         <v>46083</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="2">
         <v>28.4</v>
@@ -1566,61 +1573,61 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
@@ -2826,64 +2833,64 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="T1" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
@@ -2891,7 +2898,7 @@
         <v>46090</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>45.6</v>
@@ -2974,7 +2981,7 @@
         <v>14.7</v>
       </c>
       <c r="T6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
@@ -3003,7 +3010,7 @@
         <v>2.4</v>
       </c>
       <c r="T7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -3017,7 +3024,7 @@
         <v>31.1</v>
       </c>
       <c r="T8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
@@ -3381,7 +3388,7 @@
         <v>24.1</v>
       </c>
       <c r="T24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
@@ -4096,13 +4103,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
         <v>78</v>
-      </c>
-      <c r="B1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -4120,15 +4127,15 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -4136,10 +4143,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -4163,55 +4170,55 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="S1" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
@@ -4468,7 +4475,7 @@
         <v>2.4</v>
       </c>
       <c r="S7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -4508,7 +4515,7 @@
         <v>4.3</v>
       </c>
       <c r="S9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -4561,7 +4568,7 @@
         <v>22.2</v>
       </c>
       <c r="S11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
@@ -4680,7 +4687,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="S16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
@@ -4835,7 +4842,7 @@
         <v>11.7</v>
       </c>
       <c r="S22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -4885,7 +4892,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="S24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -4893,7 +4900,7 @@
         <v>46097</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -5025,7 +5032,7 @@
         <v>1.9</v>
       </c>
       <c r="S29" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -5125,7 +5132,7 @@
         <v>7.3</v>
       </c>
       <c r="S32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
@@ -5163,7 +5170,7 @@
         <v>11.5</v>
       </c>
       <c r="S33" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
@@ -5355,7 +5362,7 @@
         <v>3.9</v>
       </c>
       <c r="S38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
@@ -5442,7 +5449,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="S40" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -5469,46 +5476,46 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="O1" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -5534,10 +5541,13 @@
         <v>16</v>
       </c>
       <c r="O2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>46104</v>
+      </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
@@ -5549,6 +5559,9 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>46104</v>
+      </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
@@ -5563,6 +5576,9 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>46104</v>
+      </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -5586,6 +5602,9 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>46104</v>
+      </c>
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -5606,6 +5625,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>46104</v>
+      </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
@@ -5637,10 +5659,13 @@
         <v>1.5</v>
       </c>
       <c r="O7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>46104</v>
+      </c>
       <c r="B8" t="s">
         <v>21</v>
       </c>
@@ -5661,6 +5686,9 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>46104</v>
+      </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
@@ -5699,6 +5727,9 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46104</v>
+      </c>
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -5710,6 +5741,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46104</v>
+      </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
@@ -5724,6 +5758,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>46104</v>
+      </c>
       <c r="B12" t="s">
         <v>24</v>
       </c>
@@ -5738,6 +5775,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>46104</v>
+      </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
@@ -5767,6 +5807,9 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>46104</v>
+      </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -5787,6 +5830,9 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>46104</v>
+      </c>
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -5810,6 +5856,9 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>46104</v>
+      </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -5826,9 +5875,12 @@
         <v>62.2</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>46104</v>
+      </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -5846,7 +5898,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>46104</v>
+      </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
@@ -5866,7 +5921,10 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>46104</v>
+      </c>
       <c r="B19" t="s">
         <v>5</v>
       </c>
@@ -5883,10 +5941,13 @@
         <v>6.1</v>
       </c>
       <c r="O19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>46104</v>
+      </c>
       <c r="B20" t="s">
         <v>25</v>
       </c>
@@ -5897,7 +5958,10 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>46104</v>
+      </c>
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -5923,7 +5987,10 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>46104</v>
+      </c>
       <c r="B22" t="s">
         <v>31</v>
       </c>
@@ -5937,7 +6004,10 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>46104</v>
+      </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
@@ -5969,10 +6039,13 @@
         <v>25.1</v>
       </c>
       <c r="O23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>46104</v>
+      </c>
       <c r="B24" t="s">
         <v>22</v>
       </c>
@@ -6004,7 +6077,10 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>46104</v>
+      </c>
       <c r="B25" t="s">
         <v>27</v>
       </c>
@@ -6030,7 +6106,10 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>46104</v>
+      </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
@@ -6071,10 +6150,13 @@
         <v>4.8</v>
       </c>
       <c r="O26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>46104</v>
+      </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
@@ -6103,7 +6185,10 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>46104</v>
+      </c>
       <c r="B28" t="s">
         <v>34</v>
       </c>
@@ -6132,7 +6217,10 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>46104</v>
+      </c>
       <c r="B29" t="s">
         <v>8</v>
       </c>
@@ -6164,10 +6252,13 @@
         <v>16.8</v>
       </c>
       <c r="O29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>46104</v>
+      </c>
       <c r="B30" t="s">
         <v>20</v>
       </c>
@@ -6193,7 +6284,10 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>46104</v>
+      </c>
       <c r="B31" t="s">
         <v>11</v>
       </c>
@@ -6216,10 +6310,13 @@
         <v>17.7</v>
       </c>
       <c r="O31" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>46104</v>
+      </c>
       <c r="B32" t="s">
         <v>32</v>
       </c>
@@ -6248,7 +6345,10 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>46104</v>
+      </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
@@ -6283,10 +6383,13 @@
         <v>1.7</v>
       </c>
       <c r="O33" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>46104</v>
+      </c>
       <c r="B34" t="s">
         <v>13</v>
       </c>
@@ -6327,7 +6430,10 @@
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>46104</v>
+      </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
@@ -6359,7 +6465,10 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>46104</v>
+      </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
@@ -6397,7 +6506,10 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>46104</v>
+      </c>
       <c r="B37" t="s">
         <v>6</v>
       </c>
@@ -6429,10 +6541,13 @@
         <v>7.7</v>
       </c>
       <c r="O37" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>46104</v>
+      </c>
       <c r="B38" t="s">
         <v>36</v>
       </c>
@@ -6464,7 +6579,10 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>46104</v>
+      </c>
       <c r="B39" t="s">
         <v>0</v>
       </c>
@@ -6499,7 +6617,10 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>46104</v>
+      </c>
       <c r="B40" t="s">
         <v>3</v>
       </c>
@@ -6518,4 +6639,341 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26E6E076-D55A-364B-966B-1A0A8B44E81C}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A40">
+    <sortCondition ref="A2:A40"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>